--- a/output/full_scan/batch_seq8_2026-08-05.xlsx
+++ b/output/full_scan/batch_seq8_2026-08-05.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -739,21 +739,21 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7704</v>
+        <v>6969</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>622.8508064359011</v>
+        <v>699.8772037831682</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>65.3</v>
+        <v>34.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>68.24027475844798</v>
+        <v>59.85686316818917</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.90691008051951</v>
+        <v>20.43908980471903</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6.564286607563886</v>
+        <v>0.4478491967497037</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.277494083075631</v>
+        <v>0.3615532431904609</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7792</v>
+        <v>7704</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>618.9512672544814</v>
+        <v>622.8508064359011</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>203.5</v>
+        <v>65.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>40.82579271811692</v>
+        <v>68.24027475844798</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>36.43037058652852</v>
+        <v>24.90691008051951</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.091139682262708</v>
+        <v>6.564286607563886</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.7907433830229209</v>
+        <v>1.277494083075631</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6863</v>
+        <v>7792</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>614.4842530340754</v>
+        <v>618.9512672544814</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>135</v>
+        <v>203.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>79.21691176088444</v>
+        <v>40.82579271811692</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45.17365896983307</v>
+        <v>36.43037058652852</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.248425303407547</v>
+        <v>2.091139682262708</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.657468894494679</v>
+        <v>0.7907433830229209</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6958</v>
+        <v>6863</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>602.79281499176</v>
+        <v>614.4842530340754</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>18.7</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.85458813588723</v>
+        <v>79.21691176088444</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30.58968978554773</v>
+        <v>45.17365896983307</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.081425358515803</v>
+        <v>1.248425303407547</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0621493388834193</v>
+        <v>2.657468894494679</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7711</v>
+        <v>6958</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>590.1826862272578</v>
+        <v>602.79281499176</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>329</v>
+        <v>18.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.04520484671829</v>
+        <v>61.85458813588723</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>34.1066964042838</v>
+        <v>30.58968978554773</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.3970328630277459</v>
+        <v>1.081425358515803</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>3.970571518988248</v>
+        <v>0.0621493388834193</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6877</v>
+        <v>7711</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>563.1235956799314</v>
+        <v>590.1826862272578</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>125</v>
+        <v>329</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>50.0033711207096</v>
+        <v>58.04520484671829</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.62985020201733</v>
+        <v>34.1066964042838</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7535956529507335</v>
+        <v>0.3970328630277459</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.4895908592149656</v>
+        <v>3.970571518988248</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6947</v>
+        <v>6877</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>531.5553312690259</v>
+        <v>563.1235956799314</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>125</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>52.5172219913674</v>
+        <v>50.0033711207096</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.23081695809292</v>
+        <v>20.62985020201733</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.070060342031636</v>
+        <v>0.7535956529507335</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.1802027384304558</v>
+        <v>0.4895908592149656</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6957</v>
+        <v>6947</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>529.6137975189984</v>
+        <v>531.5553312690259</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>213.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>47.24857425077747</v>
+        <v>52.5172219913674</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31.32992146337221</v>
+        <v>20.23081695809292</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4803858418397245</v>
+        <v>1.070060342031636</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-4.954004749623545</v>
+        <v>0.1802027384304558</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6949</v>
+        <v>6957</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>520.0071172608141</v>
+        <v>529.6137975189984</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>958</v>
+        <v>213.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.05413472156104</v>
+        <v>47.24857425077747</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.31162909846139</v>
+        <v>31.32992146337221</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.179185290344616</v>
+        <v>0.4803858418397245</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-15.04661724212012</v>
+        <v>-4.954004749623545</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7714</v>
+        <v>6949</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>490.0279455857963</v>
+        <v>520.0071172608141</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>158</v>
+        <v>958</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>50.79760354614146</v>
+        <v>56.05413472156104</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>25.93060847308813</v>
+        <v>27.31162909846139</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.695090781405952</v>
+        <v>1.179185290344616</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-3.980672040252904</v>
+        <v>-15.04661724212012</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8040</v>
+        <v>7714</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>473.4731696209184</v>
+        <v>490.0279455857963</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>158</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>43.32100960851811</v>
+        <v>50.79760354614146</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>29.1980137578499</v>
+        <v>25.93060847308813</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7086160125209509</v>
+        <v>0.695090781405952</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.265007318521083</v>
+        <v>-3.980672040252904</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7734</v>
+        <v>8033</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>467.2296068395896</v>
+        <v>486.8034685227751</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3440</v>
+        <v>189</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>55.33547769914768</v>
+        <v>51.71346551472125</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>12.09982970504964</v>
+        <v>24.4372647897316</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.110556138258564</v>
+        <v>0.1341559127022861</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>59.02532754672355</v>
+        <v>-4.83313390553278</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6914</v>
+        <v>8040</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>465.7360194759465</v>
+        <v>473.4731696209184</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>147</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.12789964422903</v>
+        <v>43.32100960851811</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>16.64390660028056</v>
+        <v>29.1980137578499</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3001258176977305</v>
+        <v>0.7086160125209509</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1585721212757438</v>
+        <v>0.265007318521083</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7751</v>
+        <v>7734</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>462.1416841433152</v>
+        <v>467.2296068395896</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1405</v>
+        <v>3440</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.29673497373388</v>
+        <v>55.33547769914768</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.6795604537957</v>
+        <v>12.09982970504964</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.814168414331519</v>
+        <v>1.110556138258564</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>35.57181634049554</v>
+        <v>59.02532754672355</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7744</v>
+        <v>6914</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>448.5940597530968</v>
+        <v>465.7360194759465</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>444.5</v>
+        <v>147</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.07509851358268</v>
+        <v>60.12789964422903</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20.95001538400014</v>
+        <v>16.64390660028056</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.554643017972829</v>
+        <v>0.3001258176977305</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.703115653628245</v>
+        <v>0.1585721212757438</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8021</v>
+        <v>7751</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>447.462002082149</v>
+        <v>462.1416841433152</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>396</v>
+        <v>1405</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>46.39150481757028</v>
+        <v>56.29673497373388</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.74692617579748</v>
+        <v>14.6795604537957</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.737745166400478</v>
+        <v>1.814168414331519</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.9022670158996746</v>
+        <v>35.57181634049554</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7822</v>
+        <v>7610</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>446.5108411704224</v>
+        <v>448.7840872285085</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>867</v>
+        <v>1595</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45.07429409332811</v>
+        <v>44.91271690066322</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.04378550602281</v>
+        <v>32.8363918348832</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.241943602438316</v>
+        <v>0.3959606510862619</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4.296185256971427</v>
+        <v>-57.15421424811487</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8039</v>
+        <v>7744</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>442.6946566259127</v>
+        <v>448.5940597530968</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>220</v>
+        <v>444.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.94294836321138</v>
+        <v>55.07509851358268</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>25.59478626445262</v>
+        <v>20.95001538400014</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.2661474280466396</v>
+        <v>1.554643017972829</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-1.746223955032786</v>
+        <v>2.703115653628245</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6855</v>
+        <v>8021</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>421.9917173052133</v>
+        <v>447.462002082149</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>119.5</v>
+        <v>396</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.27242968489145</v>
+        <v>46.39150481757028</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6.005583607126048</v>
+        <v>24.74692617579748</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3.827152194211018</v>
+        <v>2.737745166400478</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.497630291087772</v>
+        <v>-0.9022670158996746</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7738</v>
+        <v>7822</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>421.8704903037156</v>
+        <v>446.5108411704224</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>167.5</v>
+        <v>867</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49.86304674543903</v>
+        <v>45.07429409332811</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.88410590653631</v>
+        <v>27.04378550602281</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2827145510730995</v>
+        <v>1.241943602438316</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0447695410521694</v>
+        <v>4.296185256971427</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6907</v>
+        <v>8039</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>421.3653438569573</v>
+        <v>442.6946566259127</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>177.5</v>
+        <v>220</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>48.80640373347291</v>
+        <v>59.94294836321138</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.63012314080633</v>
+        <v>25.59478626445262</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.186092898521678</v>
+        <v>0.2661474280466396</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-5.661522467025986</v>
+        <v>-1.746223955032786</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7721</v>
+        <v>6855</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>384.9363901308336</v>
+        <v>421.9917173052133</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>61.1</v>
+        <v>119.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>41.99261693143652</v>
+        <v>52.27242968489145</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>26.32527661906293</v>
+        <v>6.005583607126048</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3201272716331688</v>
+        <v>3.827152194211018</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1595530330371071</v>
+        <v>2.497630291087772</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7827</v>
+        <v>7738</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>375.6084259214829</v>
+        <v>421.8704903037156</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>156</v>
+        <v>167.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.00110193335662</v>
+        <v>49.86304674543903</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17.55898925037038</v>
+        <v>27.88410590653631</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7104462933422953</v>
+        <v>0.2827145510730995</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.2215236133270988</v>
+        <v>0.0447695410521694</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6955</v>
+        <v>6907</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>372.8092147529817</v>
+        <v>421.3653438569573</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>121</v>
+        <v>177.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.21735714526406</v>
+        <v>48.80640373347291</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>9.247089011623419</v>
+        <v>26.63012314080633</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8802318234307254</v>
+        <v>1.186092898521678</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.6535686629391666</v>
+        <v>-5.661522467025986</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7795</v>
+        <v>7721</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>370.3472195634083</v>
+        <v>384.9363901308336</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>426</v>
+        <v>61.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>48.13336362484075</v>
+        <v>41.99261693143652</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.34929202436633</v>
+        <v>26.32527661906293</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.33571271626155</v>
+        <v>0.3201272716331688</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-5.708996488949801</v>
+        <v>0.1595530330371071</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6910</v>
+        <v>7827</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>365.4593569550912</v>
+        <v>375.6084259214829</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>24.3</v>
+        <v>156</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>35.40664107835913</v>
+        <v>52.00110193335662</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26.57892555524792</v>
+        <v>17.55898925037038</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.180971043241059</v>
+        <v>0.7104462933422953</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0179096722718642</v>
+        <v>0.2215236133270988</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7740</v>
+        <v>6955</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>354.5394023423891</v>
+        <v>372.8092147529817</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>153.5</v>
+        <v>121</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.52535932960605</v>
+        <v>52.21735714526406</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.65223260365975</v>
+        <v>9.247089011623419</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9223021030554612</v>
+        <v>0.8802318234307254</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.5157001156140035</v>
+        <v>-0.6535686629391666</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7769</v>
+        <v>7795</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>351.0812690467349</v>
+        <v>370.3472195634083</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>6530</v>
+        <v>426</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52.67945161580883</v>
+        <v>48.13336362484075</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>14.09857204503144</v>
+        <v>25.34929202436633</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8258281003811593</v>
+        <v>1.33571271626155</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>51.35047049594414</v>
+        <v>-5.708996488949801</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6937</v>
+        <v>8028</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>341.4273002619711</v>
+        <v>369.9896503937877</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>47.51453087681932</v>
+        <v>48.14741724801645</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10.21042390661621</v>
+        <v>18.07107861199304</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6121722091476421</v>
+        <v>0.2963654525282232</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.9015414250891388</v>
+        <v>-3.324848389228302</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6894</v>
+        <v>6910</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>341.2616123420054</v>
+        <v>365.4593569550912</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>354</v>
+        <v>24.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>56.43821404768149</v>
+        <v>35.40664107835913</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.64501547323913</v>
+        <v>26.57892555524792</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.181280995097548</v>
+        <v>1.180971043241059</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>3.382591706025768</v>
+        <v>0.0179096722718642</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7717</v>
+        <v>7740</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>334.017260102908</v>
+        <v>354.5394023423891</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>440</v>
+        <v>153.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.55261647398363</v>
+        <v>51.52535932960605</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>27.59461822538954</v>
+        <v>14.65223260365975</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7645402392073385</v>
+        <v>0.9223021030554612</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>4.536544878134258</v>
+        <v>0.5157001156140035</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6901</v>
+        <v>7769</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>333.8377488143161</v>
+        <v>351.0812690467349</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>17.6</v>
+        <v>6530</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>51.89134594026375</v>
+        <v>52.67945161580883</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>22.73651574286482</v>
+        <v>14.09857204503144</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4675493007955843</v>
+        <v>0.8258281003811593</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.1549124003268847</v>
+        <v>51.35047049594414</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6865</v>
+        <v>6937</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>331.7026284614953</v>
+        <v>341.4273002619711</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>24.75</v>
+        <v>260</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.06148916526579</v>
+        <v>47.51453087681932</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>9.130031849420345</v>
+        <v>10.21042390661621</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.405365164286075</v>
+        <v>0.6121722091476421</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.6073492070587325</v>
+        <v>-0.9015414250891388</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6921</v>
+        <v>6894</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>326.3703511461785</v>
+        <v>341.2616123420054</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>63.8</v>
+        <v>354</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.95826415009584</v>
+        <v>56.43821404768149</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>30.69064824109919</v>
+        <v>17.64501547323913</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.15806526464133</v>
+        <v>1.181280995097548</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1143098560931341</v>
+        <v>3.382591706025768</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6965</v>
+        <v>7717</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>325.8422017930321</v>
+        <v>334.017260102908</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>76.2</v>
+        <v>440</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>40.69253790478244</v>
+        <v>49.55261647398363</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>31.60624021084189</v>
+        <v>27.59461822538954</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5762735061451291</v>
+        <v>0.7645402392073385</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.2182519488965786</v>
+        <v>4.536544878134258</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6933</v>
+        <v>6901</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>324.880437348705</v>
+        <v>333.8377488143161</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>165.5</v>
+        <v>17.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.06491791324621</v>
+        <v>51.89134594026375</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13.00344523922312</v>
+        <v>22.73651574286482</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.493784095952655</v>
+        <v>0.4675493007955843</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.3097783367754607</v>
+        <v>-0.1549124003268847</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6996</v>
+        <v>6865</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>323.4282512139754</v>
+        <v>331.7026284614953</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>180</v>
+        <v>24.75</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.17830292247713</v>
+        <v>51.06148916526579</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22.14212604088726</v>
+        <v>9.130031849420345</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.578456360879214</v>
+        <v>2.405365164286075</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.7539805857930748</v>
+        <v>0.6073492070587325</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6862</v>
+        <v>6921</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>319.1436683477032</v>
+        <v>326.3703511461785</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>144</v>
+        <v>63.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>43.94150311313344</v>
+        <v>47.95826415009584</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.40352392221948</v>
+        <v>30.69064824109919</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5405139895833939</v>
+        <v>1.15806526464133</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.6036729609110374</v>
+        <v>0.1143098560931341</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6951</v>
+        <v>6965</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>318.8757809869659</v>
+        <v>325.8422017930321</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>71.2</v>
+        <v>76.2</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>34.35416421188215</v>
+        <v>40.69253790478244</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>38.73070541097437</v>
+        <v>31.60624021084189</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.2607349799818365</v>
+        <v>0.5762735061451291</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1254989124043048</v>
+        <v>-0.2182519488965786</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6919</v>
+        <v>6933</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>318.8483977385577</v>
+        <v>324.880437348705</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>108.5</v>
+        <v>165.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.23508933596554</v>
+        <v>54.06491791324621</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.50601666140048</v>
+        <v>13.00344523922312</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6778749317283974</v>
+        <v>1.493784095952655</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.3746301897484942</v>
+        <v>0.3097783367754607</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7732</v>
+        <v>6996</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>317.8040399652664</v>
+        <v>323.4282512139754</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>35.65</v>
+        <v>180</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.75827840857004</v>
+        <v>50.17830292247713</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4.430005502299615</v>
+        <v>22.14212604088726</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.417975567190227</v>
+        <v>1.578456360879214</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.09978985824594711</v>
+        <v>0.7539805857930748</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7818</v>
+        <v>6862</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>314.8760089088942</v>
+        <v>319.1436683477032</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>62.1</v>
+        <v>144</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>27.01732445200261</v>
+        <v>43.94150311313344</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>32.13127984830199</v>
+        <v>25.40352392221948</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5291697591101093</v>
+        <v>0.5405139895833939</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.658274279431597</v>
+        <v>0.6036729609110374</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7842</v>
+        <v>6951</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>309.4939129568372</v>
+        <v>318.8757809869659</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>43.53692019702254</v>
+        <v>34.35416421188215</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11.2271616254255</v>
+        <v>38.73070541097437</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4.22009820761008</v>
+        <v>0.2607349799818365</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.2700844219242224</v>
+        <v>0.1254989124043048</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8034</v>
+        <v>6919</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>308.81416057897</v>
+        <v>318.8483977385577</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>19.55</v>
+        <v>108.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>43.54096197463086</v>
+        <v>56.23508933596554</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>37.43684813148558</v>
+        <v>15.50601666140048</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.592980008430854</v>
+        <v>0.6778749317283974</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1007033328298502</v>
+        <v>0.3746301897484942</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6903</v>
+        <v>7732</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>308.215307509732</v>
+        <v>317.8040399652664</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>319.5</v>
+        <v>35.65</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>42.24937761275994</v>
+        <v>51.75827840857004</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.81590960593929</v>
+        <v>4.430005502299615</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5808564841275093</v>
+        <v>1.417975567190227</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-3.081330333117126</v>
+        <v>-0.09978985824594711</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6890</v>
+        <v>7818</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>301.4122101819115</v>
+        <v>314.8760089088942</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>171.5</v>
+        <v>62.1</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>42.47941978733938</v>
+        <v>27.01732445200261</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.04645124189368</v>
+        <v>32.13127984830199</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.660403200213793</v>
+        <v>0.5291697591101093</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3979311835423686</v>
+        <v>-0.658274279431597</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7821</v>
+        <v>7842</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>297.7909405765357</v>
+        <v>309.4939129568372</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>40</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>39.86744354296427</v>
+        <v>43.53692019702254</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.79280672337844</v>
+        <v>11.2271616254255</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7839831649435498</v>
+        <v>4.22009820761008</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0779752596716278</v>
+        <v>-0.2700844219242224</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6895</v>
+        <v>8034</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>297.6089153762364</v>
+        <v>308.81416057897</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>118.5</v>
+        <v>19.55</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>35.28584805339034</v>
+        <v>43.54096197463086</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>29.52682368490789</v>
+        <v>37.43684813148558</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.204371423308042</v>
+        <v>0.592980008430854</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.5866808053230415</v>
+        <v>0.1007033328298502</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>7788</v>
+        <v>6903</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>291.7617079362985</v>
+        <v>308.215307509732</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>210</v>
+        <v>319.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45.69091310225143</v>
+        <v>42.24937761275994</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>25.72035114421557</v>
+        <v>22.81590960593929</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5908950501508422</v>
+        <v>0.5808564841275093</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-2.531768837355418</v>
+        <v>-3.081330333117126</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6994</v>
+        <v>6890</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>291.1216110653489</v>
+        <v>301.4122101819115</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>36.55</v>
+        <v>171.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>28.02611148019776</v>
+        <v>42.47941978733938</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>36.07443851346006</v>
+        <v>16.04645124189368</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9012900940444272</v>
+        <v>0.660403200213793</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1590903327417878</v>
+        <v>0.3979311835423686</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6869</v>
+        <v>7821</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>284.7059903148501</v>
+        <v>297.7909405765357</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>40</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45.35757732508693</v>
+        <v>39.86744354296427</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.21949802289866</v>
+        <v>19.79280672337844</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9353076230133084</v>
+        <v>0.7839831649435498</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.4047886356677965</v>
+        <v>0.0779752596716278</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6861</v>
+        <v>6895</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>284.6405609921929</v>
+        <v>297.6089153762364</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>209.5</v>
+        <v>118.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>39.04712005491552</v>
+        <v>35.28584805339034</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>31.72340008962125</v>
+        <v>29.52682368490789</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6330434454364747</v>
+        <v>1.204371423308042</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>3.189971751705286</v>
+        <v>0.5866808053230415</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6944</v>
+        <v>7788</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>283.6874345572391</v>
+        <v>291.7617079362985</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>787</v>
+        <v>210</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>42.13682743894261</v>
+        <v>45.69091310225143</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25.07714186866863</v>
+        <v>25.72035114421557</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.735807536680821</v>
+        <v>0.5908950501508422</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-11.33060474966294</v>
+        <v>-2.531768837355418</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6887</v>
+        <v>6994</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>279.6695644673804</v>
+        <v>291.1216110653489</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>37.1</v>
+        <v>36.55</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.37003555628812</v>
+        <v>28.02611148019776</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.40742950222204</v>
+        <v>36.07443851346006</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3898900550565207</v>
+        <v>0.9012900940444272</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1070252795618285</v>
+        <v>0.1590903327417878</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6902</v>
+        <v>6869</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>278.160242513975</v>
+        <v>284.7059903148501</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>123</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.05100406378439</v>
+        <v>45.35757732508693</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18.56780474713302</v>
+        <v>22.21949802289866</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8177520770819826</v>
+        <v>0.9353076230133084</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2210497993026119</v>
+        <v>0.4047886356677965</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7791</v>
+        <v>6861</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>274.8180935933948</v>
+        <v>284.6405609921929</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>59.7</v>
+        <v>209.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>32.503234644974</v>
+        <v>39.04712005491552</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.23505273875958</v>
+        <v>31.72340008962125</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7067279948402865</v>
+        <v>0.6330434454364747</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.2400071247034103</v>
+        <v>3.189971751705286</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7631</v>
+        <v>6944</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>272.6248554136304</v>
+        <v>283.6874345572391</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>133.5</v>
+        <v>787</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.64628606074928</v>
+        <v>42.13682743894261</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>11.17853387830152</v>
+        <v>25.07714186866863</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4915633113322455</v>
+        <v>0.735807536680821</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.211948602634178</v>
+        <v>-11.33060474966294</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7689</v>
+        <v>6887</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>269.4151512262029</v>
+        <v>279.6695644673804</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>167</v>
+        <v>37.1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>19.63016402521396</v>
+        <v>51.37003555628812</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.3720588290025</v>
+        <v>16.40742950222204</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.141515122620288</v>
+        <v>0.3898900550565207</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-3.316251296489918</v>
+        <v>-0.1070252795618285</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6924</v>
+        <v>6902</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>262.3076689794559</v>
+        <v>278.160242513975</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46.37574229340872</v>
+        <v>48.05100406378439</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.53523756684169</v>
+        <v>18.56780474713302</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.445927304225081</v>
+        <v>0.8177520770819826</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.824912252652215</v>
+        <v>0.2210497993026119</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8038</v>
+        <v>7791</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>259.5628656853722</v>
+        <v>274.8180935933948</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>31.9</v>
+        <v>59.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>33.3338056260591</v>
+        <v>32.503234644974</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.83963929746362</v>
+        <v>24.23505273875958</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5350637531543844</v>
+        <v>0.7067279948402865</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.4659436695473427</v>
+        <v>-0.2400071247034103</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8032</v>
+        <v>7631</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>258.7564928723023</v>
+        <v>272.6248554136304</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>36.3</v>
+        <v>133.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.12999506383742</v>
+        <v>44.64628606074928</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>34.37402937774601</v>
+        <v>11.17853387830152</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6958728455139735</v>
+        <v>0.4915633113322455</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1416302623291949</v>
+        <v>-1.211948602634178</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8042</v>
+        <v>7689</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>256.7685335107363</v>
+        <v>269.4151512262029</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>40.49976760701885</v>
+        <v>19.63016402521396</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>28.11608982803022</v>
+        <v>29.3720588290025</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.062772263289885</v>
+        <v>1.141515122620288</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-1.156387955133658</v>
+        <v>-3.316251296489918</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7722</v>
+        <v>6924</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>253.3121034969238</v>
+        <v>262.3076689794559</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>270</v>
+        <v>108</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>37.46005706220122</v>
+        <v>46.37574229340872</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>24.32704310257321</v>
+        <v>22.53523756684169</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7001677909519207</v>
+        <v>0.445927304225081</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-3.122734384981475</v>
+        <v>0.824912252652215</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6899</v>
+        <v>8038</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>252.8888318663151</v>
+        <v>259.5628656853722</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>51</v>
+        <v>31.9</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>39.45344446500983</v>
+        <v>33.3338056260591</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>26.13665698346109</v>
+        <v>20.83963929746362</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3536158149152455</v>
+        <v>0.5350637531543844</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.2029034528577149</v>
+        <v>-0.4659436695473427</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7828</v>
+        <v>8032</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>252.6679432667828</v>
+        <v>258.7564928723023</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1750</v>
+        <v>36.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.02690268899389</v>
+        <v>42.12999506383742</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19.06285310894876</v>
+        <v>34.37402937774601</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.596431075822257</v>
+        <v>0.6958728455139735</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-19.04045664756847</v>
+        <v>0.1416302623291949</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7768</v>
+        <v>8042</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>251.4633760969261</v>
+        <v>256.7685335107363</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>262</v>
+        <v>110</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>34.25042818844796</v>
+        <v>40.49976760701885</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45.2300265944293</v>
+        <v>28.11608982803022</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.38603981924232</v>
+        <v>1.062772263289885</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.354336362942764</v>
+        <v>-1.156387955133658</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7749</v>
+        <v>7722</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>250.5919727312572</v>
+        <v>253.3121034969237</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>348</v>
+        <v>270</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.76625021370664</v>
+        <v>37.46005706220122</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>35.15200266861338</v>
+        <v>24.32704310257321</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7090392566174332</v>
+        <v>0.7001677909519207</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>2.040557981141369</v>
+        <v>-3.122734384981475</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6962</v>
+        <v>6899</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>248.7600157475258</v>
+        <v>252.8888318663151</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>31.2</v>
+        <v>51</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>39.19133098871579</v>
+        <v>39.45344446500983</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>28.64561588551498</v>
+        <v>26.13665698346109</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6291405433698145</v>
+        <v>0.3536158149152455</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0541059045194511</v>
+        <v>0.2029034528577149</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7780</v>
+        <v>7828</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>246.9740905117964</v>
+        <v>252.6679432667828</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>16.6</v>
+        <v>1750</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>31.24732392870321</v>
+        <v>51.02690268899389</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>33.8169271615886</v>
+        <v>19.06285310894876</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7604769322968619</v>
+        <v>0.596431075822257</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0433262360125943</v>
+        <v>-19.04045664756847</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8043</v>
+        <v>7768</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>240.6363183301326</v>
+        <v>251.4633760969261</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>135.5</v>
+        <v>262</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.10277860567327</v>
+        <v>34.25042818844796</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>24.61348592614954</v>
+        <v>45.2300265944293</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9399181409454576</v>
+        <v>1.38603981924232</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2902841584175686</v>
+        <v>-1.354336362942764</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7712</v>
+        <v>7749</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>239.9048368086438</v>
+        <v>250.5919727312572</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>140</v>
+        <v>348</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.89036595499911</v>
+        <v>40.76625021370664</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>27.64545953989311</v>
+        <v>35.15200266861338</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6030115391788944</v>
+        <v>0.7090392566174332</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.4189740895214378</v>
+        <v>2.040557981141369</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7747</v>
+        <v>6962</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>238.6991668264886</v>
+        <v>248.7600157475258</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>116</v>
+        <v>31.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.41939837120165</v>
+        <v>39.19133098871579</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>19.29259177863643</v>
+        <v>28.64561588551498</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4772999751170629</v>
+        <v>0.6291405433698145</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-2.78535309281908</v>
+        <v>-0.0541059045194511</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6908</v>
+        <v>7780</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>236.8438931433968</v>
+        <v>246.9740905117964</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>32.85</v>
+        <v>16.6</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>29.72445205520431</v>
+        <v>31.24732392870321</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>29.1427207213732</v>
+        <v>33.8169271615886</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.356994843621994</v>
+        <v>0.7604769322968619</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.162126810213713</v>
+        <v>-0.0433262360125943</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7839</v>
+        <v>8043</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>230.1248189214999</v>
+        <v>240.6363183301326</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>45.5</v>
+        <v>135.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>48.02578164548854</v>
+        <v>43.10277860567327</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11.28676204822938</v>
+        <v>24.61348592614954</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.0650214082986823</v>
+        <v>0.9399181409454576</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.4197946436536939</v>
+        <v>-0.2902841584175686</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7728</v>
+        <v>7712</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>216.6970883617588</v>
+        <v>239.9048368086437</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>619</v>
+        <v>140</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.9710169277641</v>
+        <v>43.89036595499911</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.94603919849441</v>
+        <v>27.64545953989311</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5599985766517511</v>
+        <v>0.6030115391788944</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.202901227762084</v>
+        <v>-0.4189740895214378</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6913</v>
+        <v>7747</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>213.7389751670465</v>
+        <v>238.6991668264886</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>126.5</v>
+        <v>116</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>54.30479546358572</v>
+        <v>51.41939837120165</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.64906415586797</v>
+        <v>19.29259177863643</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.7058063683527808</v>
+        <v>0.4772999751170629</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.670885696287201</v>
+        <v>-2.78535309281908</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d</t>
+          <t>market_above_ma60, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8044</v>
+        <v>6908</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>213.3947628772269</v>
+        <v>236.8438931433968</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>26.95</v>
+        <v>32.85</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>49.99093592426149</v>
+        <v>29.72445205520431</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18.1111095613429</v>
+        <v>29.1427207213732</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9866389976197926</v>
+        <v>2.356994843621994</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.07394429443589789</v>
+        <v>-0.162126810213713</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, foreign_buy_3d, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7786</v>
+        <v>7839</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>212.6678757641317</v>
+        <v>230.1248189214999</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>124</v>
+        <v>45.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45.9906440305392</v>
+        <v>48.02578164548854</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.41660913480432</v>
+        <v>11.28676204822938</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.560993865543251</v>
+        <v>0.0650214082986823</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.70248154502529</v>
+        <v>0.4197946436536939</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7765</v>
+        <v>7728</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>212.208106668875</v>
+        <v>216.6970883617588</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>222.5</v>
+        <v>619</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>43.84375876284552</v>
+        <v>48.9710169277641</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12.05862952133651</v>
+        <v>19.94603919849441</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6801034352143019</v>
+        <v>0.5599985766517511</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.2070242439234046</v>
+        <v>1.202901227762084</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6859</v>
+        <v>6913</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>206.1677623922861</v>
+        <v>213.7389751670465</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>99.7</v>
+        <v>126.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>34.36582740763183</v>
+        <v>54.30479546358572</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>29.28889367535547</v>
+        <v>12.64906415586797</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.1570415091713389</v>
+        <v>0.7058063683527808</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.5655146025841731</v>
+        <v>0.670885696287201</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7805</v>
+        <v>8044</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>205.0926873898208</v>
+        <v>213.3947628772269</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>638</v>
+        <v>26.95</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>53.38174672978904</v>
+        <v>49.99093592426149</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>33.37743837453694</v>
+        <v>18.1111095613429</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3781240588398504</v>
+        <v>0.9866389976197926</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>5.626799371121304</v>
+        <v>0.07394429443589789</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, cci_momentum</t>
+          <t>market_above_ma60, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6931</v>
+        <v>7786</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>204.9127928535217</v>
+        <v>212.6678757641317</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>37.7</v>
+        <v>124</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.28700184170746</v>
+        <v>45.9906440305392</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>19.04119042971504</v>
+        <v>13.41660913480432</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.58485078087873</v>
+        <v>0.560993865543251</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0695464866546274</v>
+        <v>-0.70248154502529</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8016</v>
+        <v>7765</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>197.276270216401</v>
+        <v>212.208106668875</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>292.5</v>
+        <v>222.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>50.02941034172417</v>
+        <v>43.84375876284552</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.32061447697274</v>
+        <v>12.05862952133651</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8190139857431328</v>
+        <v>0.6801034352143019</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.09732595103408</v>
+        <v>0.2070242439234046</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6916</v>
+        <v>6859</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>197.1944373973252</v>
+        <v>206.1677623922861</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>18.1</v>
+        <v>99.7</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>41.55683876756278</v>
+        <v>34.36582740763183</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>16.10730220268438</v>
+        <v>29.28889367535547</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.191065807126114</v>
+        <v>0.1570415091713389</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.138553800180074</v>
+        <v>0.5655146025841731</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7705</v>
+        <v>7805</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>196.0136473635942</v>
+        <v>205.0926873898208</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>30.1</v>
+        <v>638</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.31180950348161</v>
+        <v>53.38174672978904</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.74598161734564</v>
+        <v>33.37743837453694</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9634644833379788</v>
+        <v>0.3781240588398504</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0063323262662097</v>
+        <v>5.626799371121304</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7556</v>
+        <v>6931</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>183.6367635027908</v>
+        <v>204.9127928535217</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>223.5</v>
+        <v>37.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.32561739084221</v>
+        <v>39.28700184170746</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>35.69747777792403</v>
+        <v>19.04119042971504</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3842108461213909</v>
+        <v>1.58485078087873</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.42064168141462</v>
+        <v>-0.0695464866546274</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6925</v>
+        <v>8016</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>181.196239764256</v>
+        <v>197.276270216401</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>53</v>
+        <v>292.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.15971871811912</v>
+        <v>50.02941034172417</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18.36957581689373</v>
+        <v>18.32061447697274</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7393805581110089</v>
+        <v>0.8190139857431328</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0402338649233171</v>
+        <v>-1.09732595103408</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8024</v>
+        <v>6916</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>175.4751650745523</v>
+        <v>197.1944373973252</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>14.7</v>
+        <v>18.1</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>48.83446256094154</v>
+        <v>41.55683876756278</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>21.06702181682905</v>
+        <v>16.10730220268438</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2115304465165133</v>
+        <v>1.191065807126114</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.2249875081277629</v>
+        <v>-0.138553800180074</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7799</v>
+        <v>7705</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>171.1791345413539</v>
+        <v>196.0136473635942</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>361.5</v>
+        <v>30.1</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.52548527348442</v>
+        <v>41.31180950348161</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>22.61891472968276</v>
+        <v>14.74598161734564</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.2951125800572982</v>
+        <v>0.9634644833379788</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-6.824763441894055</v>
+        <v>-0.0063323262662097</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7820</v>
+        <v>7556</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>170.9444225645382</v>
+        <v>183.6367635027908</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>100.5</v>
+        <v>223.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>35.01455623368241</v>
+        <v>44.32561739084221</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>21.24189443123512</v>
+        <v>35.69747777792403</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3853229379153265</v>
+        <v>0.3842108461213909</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.334663644848618</v>
+        <v>1.42064168141462</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7402</v>
+        <v>6925</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>170.7936617563244</v>
+        <v>181.196239764256</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46.54163434269029</v>
+        <v>41.15971871811912</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>21.98319403737717</v>
+        <v>18.36957581689373</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2948815849154572</v>
+        <v>0.7393805581110089</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>1</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.86710973375019</v>
+        <v>0.0402338649233171</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6870</v>
+        <v>8024</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>170.6339688841371</v>
+        <v>175.4751650745523</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>253</v>
+        <v>14.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45.53464339157321</v>
+        <v>48.83446256094154</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.10528039892205</v>
+        <v>21.06702181682905</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4430339020444183</v>
+        <v>0.2115304465165133</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-3.615141669852404</v>
+        <v>-0.2249875081277629</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7730</v>
+        <v>7799</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>170.0542593189949</v>
+        <v>171.1791345413539</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>160</v>
+        <v>361.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.14578039355685</v>
+        <v>43.52548527348442</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>26.5319470999869</v>
+        <v>22.61891472968276</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.103402810250592</v>
+        <v>0.2951125800572982</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.2795360352433373</v>
+        <v>-6.824763441894055</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6923</v>
+        <v>7820</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>164.8865513663703</v>
+        <v>170.9444225645382</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.61932412367779</v>
+        <v>35.01455623368241</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12.28501173163586</v>
+        <v>21.24189443123512</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.7412432994873414</v>
+        <v>0.3853229379153265</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.3679995546932835</v>
+        <v>-0.334663644848618</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6953</v>
+        <v>7402</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>162.9614836973524</v>
+        <v>170.7936617563244</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>215</v>
+        <v>106</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.24123157010714</v>
+        <v>46.54163434269029</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.78484335458546</v>
+        <v>21.98319403737717</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8943340661163881</v>
+        <v>0.2948815849154572</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>1</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0889231448209519</v>
+        <v>-1.86710973375019</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6906</v>
+        <v>6870</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>161.2213289618595</v>
+        <v>170.6339688841371</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>253</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.83063900191121</v>
+        <v>45.53464339157321</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>32.48189842987411</v>
+        <v>19.10528039892205</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.228603216784314</v>
+        <v>0.4430339020444183</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.3677838866588425</v>
+        <v>-3.615141669852404</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7736</v>
+        <v>7730</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>154.8871400845453</v>
+        <v>170.0542593189949</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>160</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.95423532366366</v>
+        <v>45.14578039355685</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>21.68225420595594</v>
+        <v>26.5319470999869</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.08871400845452369</v>
+        <v>1.103402810250592</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0349543612620587</v>
+        <v>-0.2795360352433373</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7803</v>
+        <v>6923</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>152.2724283160683</v>
+        <v>164.8865513663703</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>19.75</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>35.54227516317405</v>
+        <v>40.61932412367779</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>23.52084356812354</v>
+        <v>12.28501173163586</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4748900220497219</v>
+        <v>0.7412432994873414</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.07055118601550429</v>
+        <v>-0.3679995546932835</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6967</v>
+        <v>6953</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>149.0310499214177</v>
+        <v>162.9614836973524</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>46.22072981932428</v>
+        <v>47.24123157010714</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.6391718227786</v>
+        <v>11.78484335458546</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2628408228836628</v>
+        <v>0.8943340661163881</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>1</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.5540927756384531</v>
+        <v>0.0889231448209519</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6873</v>
+        <v>6906</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>148.3272789338316</v>
+        <v>161.2213289618595</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>78</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>39.64680252984448</v>
+        <v>41.83063900191121</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>16.86695508166051</v>
+        <v>32.48189842987411</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6654931928804994</v>
+        <v>1.228603216784314</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.7519636243796404</v>
+        <v>0.3677838866588425</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7547</v>
+        <v>7736</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>135.6363327816182</v>
+        <v>154.8871400845453</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>48.4</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>36.36180532849505</v>
+        <v>39.95423532366366</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>27.61461463535984</v>
+        <v>21.68225420595594</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6450556082420899</v>
+        <v>0.08871400845452369</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.2400522575242751</v>
+        <v>0.0349543612620587</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6997</v>
+        <v>7803</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>135.0236281865093</v>
+        <v>152.2724283160683</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>73</v>
+        <v>19.75</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>53.12645023629345</v>
+        <v>35.54227516317405</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.19051517285971</v>
+        <v>23.52084356812354</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>3.467589595910225</v>
+        <v>0.4748900220497219</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>3.021948037613237</v>
+        <v>-0.07055118601550429</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6885</v>
+        <v>6967</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>134.5617664157855</v>
+        <v>149.0310499214177</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>20.85</v>
+        <v>70</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45.2418096919036</v>
+        <v>46.22072981932428</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.04876889324399</v>
+        <v>16.6391718227786</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.8055250956777269</v>
+        <v>0.2628408228836628</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0435461926198642</v>
+        <v>-0.5540927756384531</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7823</v>
+        <v>6873</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>133.9163888915302</v>
+        <v>148.3272789338316</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>84.5</v>
+        <v>78</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>54.8920119975716</v>
+        <v>39.64680252984448</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>19.10662227234931</v>
+        <v>16.86695508166051</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.112170223233504</v>
+        <v>0.6654931928804994</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1857648094687802</v>
+        <v>-0.7519636243796404</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6971</v>
+        <v>7547</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>132.06290757786</v>
+        <v>135.6363327816182</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>25.6</v>
+        <v>48.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>32.58354376112602</v>
+        <v>36.36180532849505</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.18325713062919</v>
+        <v>27.61461463535984</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5851575336760887</v>
+        <v>0.6450556082420899</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.1287897133790264</v>
+        <v>-0.2400522575242751</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7772</v>
+        <v>6997</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>130.2716835715946</v>
+        <v>135.0236281865093</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>92.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>36.74634594005903</v>
+        <v>53.12645023629345</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>30.53354759657429</v>
+        <v>12.19051517285971</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.421629592010457</v>
+        <v>3.467589595910225</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>1.109108249258135</v>
+        <v>3.021948037613237</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>volume_break, market_above_ma60, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6934</v>
+        <v>6885</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>127.5420480631471</v>
+        <v>134.5617664157855</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>74.8</v>
+        <v>20.85</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.95832094496036</v>
+        <v>45.2418096919036</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.72517129937732</v>
+        <v>11.04876889324399</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7773777192284365</v>
+        <v>0.8055250956777269</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.65910783000663</v>
+        <v>0.0435461926198642</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7770</v>
+        <v>7823</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>126.3681313651824</v>
+        <v>133.9163888915302</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0</v>
+        <v>84.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>30.45468969688514</v>
+        <v>54.8920119975716</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.53138436980299</v>
+        <v>19.10662227234931</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0</v>
+        <v>1.112170223233504</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-3.462295101384121</v>
+        <v>0.1857648094687802</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7703</v>
+        <v>6971</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>123.3776111581436</v>
+        <v>132.06290757786</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>171.5</v>
+        <v>25.6</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.25446693592778</v>
+        <v>32.58354376112602</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>24.69867598723586</v>
+        <v>16.18325713062919</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.334655830379198</v>
+        <v>0.5851575336760887</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-1.070349198818946</v>
+        <v>-0.1287897133790264</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8011</v>
+        <v>7772</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>114.5716414940955</v>
+        <v>130.2716835715946</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>16.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>48.60977732458432</v>
+        <v>36.74634594005903</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>29.34659275036524</v>
+        <v>30.53354759657429</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.99865069885325</v>
+        <v>1.421629592010457</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.08958463823566661</v>
+        <v>1.109108249258135</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7753</v>
+        <v>6934</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>114.1778253027242</v>
+        <v>127.5420480631471</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>37.2</v>
+        <v>74.8</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>37.361461207245</v>
+        <v>48.95832094496036</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.66838428690605</v>
+        <v>16.72517129937732</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.7780621319125455</v>
+        <v>0.7773777192284365</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2536130919258019</v>
+        <v>-0.65910783000663</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7760</v>
+        <v>7770</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>111.1493771130251</v>
+        <v>126.3681313651824</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>33.15</v>
+        <v>0</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>39.8309594545321</v>
+        <v>30.45468969688514</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17.37290092945813</v>
+        <v>14.53138436980299</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.016864697714124</v>
+        <v>0</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.173678122368371</v>
+        <v>-3.462295101384121</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6854</v>
+        <v>7703</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>109.423012315367</v>
+        <v>123.3776111581436</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>96.40000000000001</v>
+        <v>171.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>39.41844592140885</v>
+        <v>42.25446693592778</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>43.20353203255216</v>
+        <v>24.69867598723586</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7368529690207922</v>
+        <v>1.334655830379198</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.7866836940488842</v>
+        <v>-1.070349198818946</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6983</v>
+        <v>8011</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>102.0867455320182</v>
+        <v>114.5716414940955</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>311</v>
+        <v>16.7</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>42.05761290409965</v>
+        <v>48.60977732458432</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.10505807124115</v>
+        <v>29.34659275036524</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.242823326821915</v>
+        <v>0.99865069885325</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.9026583475426548</v>
+        <v>0.08958463823566661</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6909</v>
+        <v>7753</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>101.8846532817622</v>
+        <v>114.1778253027242</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>41.15</v>
+        <v>37.2</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.12807559152776</v>
+        <v>37.361461207245</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>31.05942386938322</v>
+        <v>15.66838428690605</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.4281120109605289</v>
+        <v>0.7780621319125455</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0583189565179296</v>
+        <v>-0.2536130919258019</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6918</v>
+        <v>7760</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>94.22651238402337</v>
+        <v>111.1493771130251</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>33.15</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>49.59986196772962</v>
+        <v>39.8309594545321</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.33818310122726</v>
+        <v>17.37290092945813</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.7569268799650578</v>
+        <v>1.016864697714124</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0729838482926868</v>
+        <v>-0.173678122368371</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6936</v>
+        <v>6854</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>93.81246914558648</v>
+        <v>109.423012315367</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>31.75</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>40.87540778154431</v>
+        <v>39.41844592140885</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.36151395130289</v>
+        <v>43.20353203255216</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5810204169724177</v>
+        <v>0.7368529690207922</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0361199304589056</v>
+        <v>0.7866836940488842</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6988</v>
+        <v>6983</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>87.18986102735424</v>
+        <v>102.0867455320182</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>11.9</v>
+        <v>311</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>48.60784468158165</v>
+        <v>42.05761290409965</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.03343504188982</v>
+        <v>13.10505807124115</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4346437843431279</v>
+        <v>1.242823326821915</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.1290279518019119</v>
+        <v>-0.9026583475426548</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6928</v>
+        <v>6909</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>83.21026424913823</v>
+        <v>101.8846532817622</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>49.3</v>
+        <v>41.15</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>47.55924245282197</v>
+        <v>39.12807559152776</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>20.20844035002094</v>
+        <v>31.05942386938322</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.265884939961948</v>
+        <v>0.4281120109605289</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.5435032544253861</v>
+        <v>-0.0583189565179296</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,52 +7046,264 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>6918</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>愛派司</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>94.22651238402337</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>49.59986196772962</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>14.33818310122726</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.7569268799650578</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.0729838482926868</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6936</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>永鴻生技</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>93.81246914558648</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>40.87540778154431</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>14.36151395130289</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.5810204169724177</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0.0361199304589056</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6988</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>威力暘-創</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>87.18986102735424</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>48.60784468158165</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>12.03343504188982</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.4346437843431279</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.1290279518019119</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>6928</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>攸泰科技</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>83.21026424913823</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>47.55924245282197</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>20.20844035002094</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.265884939961948</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-0.5435032544253861</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>7810</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>捷創科技</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>34.28922502308438</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>189.5</v>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
         <v>45.37692208090304</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>15.31137612273437</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>0.7407267964324</v>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>-0.0511748915768563</v>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60</t>
         </is>
